--- a/data/xlsx/weab--graphic-design-ad-entrepreneurship-development.xlsx
+++ b/data/xlsx/weab--graphic-design-ad-entrepreneurship-development.xlsx
@@ -645,7 +645,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -667,7 +669,9 @@
       <c r="C17" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -689,7 +693,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -711,7 +717,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -733,7 +741,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -755,7 +765,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -777,7 +789,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -799,7 +813,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -821,7 +837,9 @@
       <c r="C24" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
